--- a/AAII_Financials/Yearly/DOW_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOW_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
   <si>
     <t>DOW</t>
   </si>
@@ -656,96 +656,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>44622000</v>
+      </c>
+      <c r="E8" s="3">
         <v>56902000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>54968000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>38542000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>42951000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>49604000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>43730000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>48158000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -755,36 +758,39 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>39742000</v>
+      </c>
+      <c r="E9" s="3">
         <v>48338000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>44191000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>33329000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>36657000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>88779000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>79962000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>37668000</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -794,36 +800,39 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4880000</v>
+      </c>
+      <c r="E10" s="3">
         <v>8564000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10777000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5213000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6294000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-39175000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-36232000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10490000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -833,9 +842,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,35 +863,36 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>829000</v>
+      </c>
+      <c r="E12" s="3">
         <v>851000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>857000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>768000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>765000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>800000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>803000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1593000</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -889,9 +902,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -928,36 +944,39 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>515000</v>
+      </c>
+      <c r="E14" s="3">
         <v>62000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>496000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>395000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4587000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1346000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3310000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2057000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -967,36 +986,39 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>324000</v>
+      </c>
+      <c r="E15" s="3">
         <v>336000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>388000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>401000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>419000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1091000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1024000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>544000</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1006,9 +1028,12 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1021,35 +1046,36 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>43037000</v>
+      </c>
+      <c r="E17" s="3">
         <v>51262000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>47561000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>36364000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>44018000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>45471000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>42658000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>44815000</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1059,36 +1085,39 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1585000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5640000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7407000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2178000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1067000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4133000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1072000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3343000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1098,9 +1127,12 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1116,35 +1148,36 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-183000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1112000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1469000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>771000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>753000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>679000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>79000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1928000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1154,33 +1187,36 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4013000</v>
+      </c>
+      <c r="E21" s="3">
         <v>9510000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11718000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5823000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2624000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7721000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3697000</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1193,36 +1229,39 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>746000</v>
+      </c>
+      <c r="E22" s="3">
         <v>662000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>731000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>878000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>933000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1063000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>914000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>858000</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1232,36 +1271,39 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>656000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6090000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8145000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2071000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1247000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3749000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>237000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4413000</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1271,36 +1313,39 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1450000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1740000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>777000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>470000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>809000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1524000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9000</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1310,9 +1355,12 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1349,36 +1397,39 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>660000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4640000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6405000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1294000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1717000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2940000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1287000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4404000</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1388,36 +1439,39 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>578000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4558000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6279000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1216000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1804000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2806000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1417000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3978000</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1427,9 +1481,12 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1466,33 +1523,36 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>445000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>1835000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>1882000</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1505,9 +1565,12 @@
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1544,9 +1607,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1583,36 +1649,39 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>183000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1112000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1469000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-771000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-753000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-679000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-79000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1928000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1622,36 +1691,39 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>578000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4558000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6279000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1216000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1359000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4641000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>465000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3978000</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1661,9 +1733,12 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1700,36 +1775,39 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>578000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4558000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6279000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1216000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1359000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4641000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>465000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3978000</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1739,53 +1817,59 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1801,8 +1885,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1818,29 +1903,30 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2987000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3886000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2988000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5104000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2367000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2724000</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1856,9 +1942,12 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1871,15 +1960,15 @@
       <c r="F42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3">
         <v>21000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>100000</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1895,30 +1984,33 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>7857000</v>
+        <v>6627000</v>
       </c>
       <c r="E43" s="3">
-        <v>9633000</v>
+        <v>7803000</v>
       </c>
       <c r="F43" s="3">
-        <v>7452000</v>
+        <v>9588000</v>
       </c>
       <c r="G43" s="3">
+        <v>7448000</v>
+      </c>
+      <c r="H43" s="3">
         <v>7596000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9054000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1934,30 +2026,33 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6076000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6988000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7372000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5701000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6214000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>16159000</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1973,30 +2068,33 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1746000</v>
+        <v>1924000</v>
       </c>
       <c r="E45" s="3">
-        <v>855000</v>
+        <v>1800000</v>
       </c>
       <c r="F45" s="3">
-        <v>827000</v>
+        <v>900000</v>
       </c>
       <c r="G45" s="3">
+        <v>831000</v>
+      </c>
+      <c r="H45" s="3">
         <v>617000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21445000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2012,30 +2110,33 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17614000</v>
+      </c>
+      <c r="E46" s="3">
         <v>20477000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20848000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19084000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16815000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>39370000</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2051,30 +2152,33 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4449000</v>
+      </c>
+      <c r="E47" s="3">
         <v>5064000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5742000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4578000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5059000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6327000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2090,30 +2194,33 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22386000</v>
+      </c>
+      <c r="E48" s="3">
         <v>21669000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21967000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22095000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23068000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21418000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2129,30 +2236,33 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10713000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11086000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11645000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12260000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12555000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18984000</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2168,9 +2278,12 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2207,9 +2320,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2246,30 +2362,33 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2805000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2307000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2788000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3453000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3027000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3309000</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,9 +2404,12 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2324,30 +2446,33 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>57967000</v>
+      </c>
+      <c r="E54" s="3">
         <v>60603000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>62990000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>61470000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>60524000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>83699000</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2363,9 +2488,12 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2381,8 +2509,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2398,29 +2527,30 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4529000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4940000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5577000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3763000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3889000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4456000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2436,30 +2566,33 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E58" s="3">
         <v>724000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>392000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>616000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1021000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>636000</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2475,30 +2608,33 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5249000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5667000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7257000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6729000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5769000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14066000</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2514,30 +2650,33 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9957000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11331000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13226000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11108000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10679000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15547000</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2553,30 +2692,33 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14907000</v>
+      </c>
+      <c r="E61" s="3">
         <v>14698000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14280000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16491000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15975000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19253000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2592,30 +2734,33 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13995000</v>
+      </c>
+      <c r="E62" s="3">
         <v>13327000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16745000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20866000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>19776000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>20646000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2631,9 +2776,12 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2670,9 +2818,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2709,9 +2860,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2748,30 +2902,33 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>39360000</v>
+      </c>
+      <c r="E66" s="3">
         <v>39885000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>44825000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>49035000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>46983000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>51216000</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2787,9 +2944,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2805,8 +2965,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2843,9 +3004,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2882,9 +3046,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2921,9 +3088,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2960,30 +3130,33 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>21774000</v>
+      </c>
+      <c r="E72" s="3">
         <v>23180000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20623000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16361000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17045000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>35460000</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2999,9 +3172,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3038,9 +3214,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3077,9 +3256,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3116,30 +3298,33 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18607000</v>
+      </c>
+      <c r="E76" s="3">
         <v>20718000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18165000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12435000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13541000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>32483000</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3155,9 +3340,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3194,80 +3382,86 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>578000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4558000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6279000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1216000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1359000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4641000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>465000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3978000</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3277,9 +3471,12 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3295,32 +3492,33 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2611000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2758000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2842000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2874000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2938000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2909000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2546000</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3333,9 +3531,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3372,9 +3573,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3411,9 +3615,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3450,9 +3657,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3489,9 +3699,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3528,33 +3741,36 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5196000</v>
+      </c>
+      <c r="E89" s="3">
         <v>7475000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7009000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6226000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5930000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4254000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4929000</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3567,9 +3783,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3585,32 +3804,33 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2363000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1830000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2195000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1257000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1970000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2117000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2994000</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,9 +3843,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3662,9 +3885,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3701,33 +3927,36 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2928000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2970000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2914000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-841000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2192000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2195000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>7518000</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3740,9 +3969,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3758,26 +3990,27 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-1972000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-2006000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-2073000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2071000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-2085000</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -3796,9 +4029,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3835,9 +4071,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3874,9 +4113,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3913,33 +4155,36 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3115000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3361000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6071000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2764000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4095000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5404000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3325000</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3952,33 +4197,36 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-45000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-237000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-99000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>107000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-27000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-99000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>320000</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3991,33 +4239,36 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-892000</v>
+      </c>
+      <c r="E102" s="3">
         <v>907000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2075000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2728000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-384000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3444000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-416000</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4030,7 +4281,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/DOW_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOW_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
   <si>
     <t>DOW</t>
   </si>
@@ -662,9 +662,7 @@
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -768,25 +766,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>39742000</v>
+        <v>39565000</v>
       </c>
       <c r="E9" s="3">
-        <v>48338000</v>
+        <v>48450000</v>
       </c>
       <c r="F9" s="3">
-        <v>44191000</v>
+        <v>44258000</v>
       </c>
       <c r="G9" s="3">
-        <v>33329000</v>
+        <v>33346000</v>
       </c>
       <c r="H9" s="3">
-        <v>36657000</v>
+        <v>36582000</v>
       </c>
       <c r="I9" s="3">
-        <v>88779000</v>
+        <v>41074000</v>
       </c>
       <c r="J9" s="3">
-        <v>79962000</v>
+        <v>36350000</v>
       </c>
       <c r="K9" s="3">
         <v>37668000</v>
@@ -810,25 +808,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>4880000</v>
+        <v>5057000</v>
       </c>
       <c r="E10" s="3">
-        <v>8564000</v>
+        <v>8452000</v>
       </c>
       <c r="F10" s="3">
-        <v>10777000</v>
+        <v>10710000</v>
       </c>
       <c r="G10" s="3">
-        <v>5213000</v>
+        <v>5196000</v>
       </c>
       <c r="H10" s="3">
-        <v>6294000</v>
+        <v>6369000</v>
       </c>
       <c r="I10" s="3">
-        <v>-39175000</v>
+        <v>8530000</v>
       </c>
       <c r="J10" s="3">
-        <v>-36232000</v>
+        <v>7380000</v>
       </c>
       <c r="K10" s="3">
         <v>10490000</v>
@@ -954,25 +952,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>515000</v>
+        <v>1128000</v>
       </c>
       <c r="E14" s="3">
-        <v>62000</v>
+        <v>-465000</v>
       </c>
       <c r="F14" s="3">
-        <v>496000</v>
+        <v>308000</v>
       </c>
       <c r="G14" s="3">
-        <v>395000</v>
+        <v>-197000</v>
       </c>
       <c r="H14" s="3">
-        <v>4587000</v>
+        <v>4305000</v>
       </c>
       <c r="I14" s="3">
-        <v>1346000</v>
+        <v>1436000</v>
       </c>
       <c r="J14" s="3">
-        <v>3310000</v>
+        <v>3016000</v>
       </c>
       <c r="K14" s="3">
         <v>2057000</v>
@@ -1011,10 +1009,10 @@
         <v>419000</v>
       </c>
       <c r="I15" s="3">
-        <v>1091000</v>
+        <v>469000</v>
       </c>
       <c r="J15" s="3">
-        <v>1024000</v>
+        <v>400000</v>
       </c>
       <c r="K15" s="3">
         <v>544000</v>
@@ -1053,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>43037000</v>
+        <v>41987000</v>
       </c>
       <c r="E17" s="3">
-        <v>51262000</v>
+        <v>50970000</v>
       </c>
       <c r="F17" s="3">
-        <v>47561000</v>
+        <v>46816000</v>
       </c>
       <c r="G17" s="3">
-        <v>36364000</v>
+        <v>35883000</v>
       </c>
       <c r="H17" s="3">
-        <v>44018000</v>
+        <v>39151000</v>
       </c>
       <c r="I17" s="3">
-        <v>45471000</v>
+        <v>44002000</v>
       </c>
       <c r="J17" s="3">
-        <v>42658000</v>
+        <v>40024000</v>
       </c>
       <c r="K17" s="3">
         <v>44815000</v>
@@ -1095,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1585000</v>
+        <v>2635000</v>
       </c>
       <c r="E18" s="3">
-        <v>5640000</v>
+        <v>5932000</v>
       </c>
       <c r="F18" s="3">
-        <v>7407000</v>
+        <v>8152000</v>
       </c>
       <c r="G18" s="3">
-        <v>2178000</v>
+        <v>2659000</v>
       </c>
       <c r="H18" s="3">
-        <v>-1067000</v>
+        <v>3800000</v>
       </c>
       <c r="I18" s="3">
-        <v>4133000</v>
+        <v>5602000</v>
       </c>
       <c r="J18" s="3">
-        <v>1072000</v>
+        <v>3706000</v>
       </c>
       <c r="K18" s="3">
         <v>3343000</v>
@@ -1155,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-183000</v>
+        <v>334000</v>
       </c>
       <c r="E20" s="3">
-        <v>1112000</v>
+        <v>-182000</v>
       </c>
       <c r="F20" s="3">
-        <v>1469000</v>
+        <v>-977000</v>
       </c>
       <c r="G20" s="3">
-        <v>771000</v>
+        <v>-4000</v>
       </c>
       <c r="H20" s="3">
-        <v>753000</v>
+        <v>-110000</v>
       </c>
       <c r="I20" s="3">
-        <v>679000</v>
+        <v>-564000</v>
       </c>
       <c r="J20" s="3">
-        <v>79000</v>
+        <v>-395000</v>
       </c>
       <c r="K20" s="3">
         <v>1928000</v>
@@ -1197,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4013000</v>
+        <v>2625000</v>
       </c>
       <c r="E21" s="3">
-        <v>9510000</v>
+        <v>6450000</v>
       </c>
       <c r="F21" s="3">
-        <v>11718000</v>
+        <v>9517000</v>
       </c>
       <c r="G21" s="3">
-        <v>5823000</v>
+        <v>3064000</v>
       </c>
       <c r="H21" s="3">
-        <v>2624000</v>
+        <v>4329000</v>
       </c>
       <c r="I21" s="3">
-        <v>7721000</v>
+        <v>6635000</v>
       </c>
       <c r="J21" s="3">
-        <v>3697000</v>
+        <v>4501000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1248,7 +1246,7 @@
         <v>731000</v>
       </c>
       <c r="G22" s="3">
-        <v>878000</v>
+        <v>827000</v>
       </c>
       <c r="H22" s="3">
         <v>933000</v>
@@ -1461,13 +1459,13 @@
         <v>1216000</v>
       </c>
       <c r="H27" s="3">
-        <v>-1804000</v>
+        <v>-1365000</v>
       </c>
       <c r="I27" s="3">
-        <v>2806000</v>
+        <v>4641000</v>
       </c>
       <c r="J27" s="3">
-        <v>-1417000</v>
+        <v>451000</v>
       </c>
       <c r="K27" s="3">
         <v>3978000</v>
@@ -1532,11 +1530,11 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1659,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>183000</v>
+        <v>-334000</v>
       </c>
       <c r="E32" s="3">
-        <v>-1112000</v>
+        <v>182000</v>
       </c>
       <c r="F32" s="3">
-        <v>-1469000</v>
+        <v>977000</v>
       </c>
       <c r="G32" s="3">
-        <v>-771000</v>
+        <v>4000</v>
       </c>
       <c r="H32" s="3">
-        <v>-753000</v>
+        <v>110000</v>
       </c>
       <c r="I32" s="3">
-        <v>-679000</v>
+        <v>564000</v>
       </c>
       <c r="J32" s="3">
-        <v>-79000</v>
+        <v>395000</v>
       </c>
       <c r="K32" s="3">
         <v>-1928000</v>
@@ -1701,16 +1699,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>578000</v>
+        <v>589000</v>
       </c>
       <c r="E33" s="3">
-        <v>4558000</v>
+        <v>4582000</v>
       </c>
       <c r="F33" s="3">
-        <v>6279000</v>
+        <v>6311000</v>
       </c>
       <c r="G33" s="3">
-        <v>1216000</v>
+        <v>1225000</v>
       </c>
       <c r="H33" s="3">
         <v>-1359000</v>
@@ -1785,16 +1783,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>578000</v>
+        <v>589000</v>
       </c>
       <c r="E35" s="3">
-        <v>4558000</v>
+        <v>4582000</v>
       </c>
       <c r="F35" s="3">
-        <v>6279000</v>
+        <v>6311000</v>
       </c>
       <c r="G35" s="3">
-        <v>1216000</v>
+        <v>1225000</v>
       </c>
       <c r="H35" s="3">
         <v>-1359000</v>
@@ -1951,26 +1949,26 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>1301000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1044000</v>
+      </c>
+      <c r="F42" s="3">
+        <v>246000</v>
+      </c>
+      <c r="G42" s="3">
+        <v>45000</v>
       </c>
       <c r="H42" s="3">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="I42" s="3">
         <v>100000</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -2003,7 +2001,7 @@
         <v>9588000</v>
       </c>
       <c r="G43" s="3">
-        <v>7448000</v>
+        <v>7709000</v>
       </c>
       <c r="H43" s="3">
         <v>7596000</v>
@@ -2051,7 +2049,7 @@
         <v>6214000</v>
       </c>
       <c r="I44" s="3">
-        <v>16159000</v>
+        <v>6899000</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
@@ -2078,22 +2076,22 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1924000</v>
+        <v>562000</v>
       </c>
       <c r="E45" s="3">
-        <v>1800000</v>
+        <v>702000</v>
       </c>
       <c r="F45" s="3">
-        <v>900000</v>
+        <v>609000</v>
       </c>
       <c r="G45" s="3">
-        <v>831000</v>
+        <v>521000</v>
       </c>
       <c r="H45" s="3">
-        <v>617000</v>
+        <v>596000</v>
       </c>
       <c r="I45" s="3">
-        <v>21445000</v>
+        <v>20553000</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -2162,22 +2160,22 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4449000</v>
+        <v>4448000</v>
       </c>
       <c r="E47" s="3">
-        <v>5064000</v>
+        <v>5048000</v>
       </c>
       <c r="F47" s="3">
-        <v>5742000</v>
+        <v>5716000</v>
       </c>
       <c r="G47" s="3">
-        <v>4578000</v>
+        <v>4608000</v>
       </c>
       <c r="H47" s="3">
-        <v>5059000</v>
+        <v>5055000</v>
       </c>
       <c r="I47" s="3">
-        <v>6327000</v>
+        <v>6326000</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
@@ -2261,10 +2259,10 @@
         <v>12555000</v>
       </c>
       <c r="I49" s="3">
-        <v>18984000</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>14071000</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2372,22 +2370,22 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2805000</v>
+        <v>895000</v>
       </c>
       <c r="E52" s="3">
-        <v>2307000</v>
+        <v>1035000</v>
       </c>
       <c r="F52" s="3">
-        <v>2788000</v>
+        <v>35000</v>
       </c>
       <c r="G52" s="3">
-        <v>3453000</v>
+        <v>23000</v>
       </c>
       <c r="H52" s="3">
-        <v>3027000</v>
+        <v>25000</v>
       </c>
       <c r="I52" s="3">
-        <v>3309000</v>
+        <v>17000</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2534,22 +2532,22 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4529000</v>
+        <v>6326000</v>
       </c>
       <c r="E57" s="3">
-        <v>4940000</v>
+        <v>7216000</v>
       </c>
       <c r="F57" s="3">
-        <v>5577000</v>
+        <v>8416000</v>
       </c>
       <c r="G57" s="3">
-        <v>3763000</v>
+        <v>5889000</v>
       </c>
       <c r="H57" s="3">
-        <v>3889000</v>
+        <v>5953000</v>
       </c>
       <c r="I57" s="3">
-        <v>4456000</v>
+        <v>6935000</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
@@ -2576,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>179000</v>
+        <v>530000</v>
       </c>
       <c r="E58" s="3">
-        <v>724000</v>
+        <v>1011000</v>
       </c>
       <c r="F58" s="3">
-        <v>392000</v>
+        <v>784000</v>
       </c>
       <c r="G58" s="3">
-        <v>616000</v>
+        <v>1036000</v>
       </c>
       <c r="H58" s="3">
-        <v>1021000</v>
+        <v>1574000</v>
       </c>
       <c r="I58" s="3">
         <v>636000</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2618,22 +2616,22 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5249000</v>
+        <v>758000</v>
       </c>
       <c r="E59" s="3">
-        <v>5667000</v>
+        <v>700000</v>
       </c>
       <c r="F59" s="3">
-        <v>7257000</v>
+        <v>1394000</v>
       </c>
       <c r="G59" s="3">
-        <v>6729000</v>
+        <v>1979000</v>
       </c>
       <c r="H59" s="3">
-        <v>5769000</v>
+        <v>1370000</v>
       </c>
       <c r="I59" s="3">
-        <v>14066000</v>
+        <v>5716000</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2702,22 +2700,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14907000</v>
+        <v>15939000</v>
       </c>
       <c r="E61" s="3">
-        <v>14698000</v>
+        <v>15695000</v>
       </c>
       <c r="F61" s="3">
-        <v>14280000</v>
+        <v>15491000</v>
       </c>
       <c r="G61" s="3">
-        <v>16491000</v>
+        <v>18190000</v>
       </c>
       <c r="H61" s="3">
-        <v>15975000</v>
+        <v>17865000</v>
       </c>
       <c r="I61" s="3">
-        <v>19253000</v>
+        <v>19317000</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2744,22 +2742,22 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>13995000</v>
+        <v>5990000</v>
       </c>
       <c r="E62" s="3">
-        <v>13327000</v>
+        <v>5687000</v>
       </c>
       <c r="F62" s="3">
-        <v>16745000</v>
+        <v>5546000</v>
       </c>
       <c r="G62" s="3">
-        <v>20866000</v>
+        <v>5199000</v>
       </c>
       <c r="H62" s="3">
-        <v>19776000</v>
+        <v>5849000</v>
       </c>
       <c r="I62" s="3">
-        <v>20646000</v>
+        <v>4469000</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -2912,22 +2910,22 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>39360000</v>
+        <v>38859000</v>
       </c>
       <c r="E66" s="3">
-        <v>39885000</v>
+        <v>39356000</v>
       </c>
       <c r="F66" s="3">
-        <v>44825000</v>
+        <v>44251000</v>
       </c>
       <c r="G66" s="3">
-        <v>49035000</v>
+        <v>48465000</v>
       </c>
       <c r="H66" s="3">
-        <v>46983000</v>
+        <v>46430000</v>
       </c>
       <c r="I66" s="3">
-        <v>51216000</v>
+        <v>50078000</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
@@ -3439,16 +3437,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>578000</v>
+        <v>589000</v>
       </c>
       <c r="E81" s="3">
-        <v>4558000</v>
+        <v>4582000</v>
       </c>
       <c r="F81" s="3">
-        <v>6279000</v>
+        <v>6311000</v>
       </c>
       <c r="G81" s="3">
-        <v>1216000</v>
+        <v>1225000</v>
       </c>
       <c r="H81" s="3">
         <v>-1359000</v>
@@ -3499,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2611000</v>
+        <v>2217000</v>
       </c>
       <c r="E83" s="3">
-        <v>2758000</v>
+        <v>2342000</v>
       </c>
       <c r="F83" s="3">
-        <v>2842000</v>
+        <v>2364000</v>
       </c>
       <c r="G83" s="3">
-        <v>2874000</v>
+        <v>2377000</v>
       </c>
       <c r="H83" s="3">
-        <v>2938000</v>
+        <v>2423000</v>
       </c>
       <c r="I83" s="3">
-        <v>2909000</v>
+        <v>2347000</v>
       </c>
       <c r="J83" s="3">
-        <v>2546000</v>
+        <v>2064000</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3811,25 +3809,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2363000</v>
+        <v>-2692000</v>
       </c>
       <c r="E91" s="3">
-        <v>-1830000</v>
+        <v>-2248000</v>
       </c>
       <c r="F91" s="3">
-        <v>-2195000</v>
+        <v>-2416000</v>
       </c>
       <c r="G91" s="3">
-        <v>-1257000</v>
+        <v>-1392000</v>
       </c>
       <c r="H91" s="3">
-        <v>-1970000</v>
+        <v>-2046000</v>
       </c>
       <c r="I91" s="3">
-        <v>-2117000</v>
+        <v>-2251000</v>
       </c>
       <c r="J91" s="3">
-        <v>-2994000</v>
+        <v>-3115000</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3997,25 +3995,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1972000</v>
+        <v>1972000</v>
       </c>
       <c r="E96" s="3">
-        <v>-2006000</v>
+        <v>2006000</v>
       </c>
       <c r="F96" s="3">
-        <v>-2073000</v>
+        <v>2073000</v>
       </c>
       <c r="G96" s="3">
-        <v>-2071000</v>
+        <v>2071000</v>
       </c>
       <c r="H96" s="3">
-        <v>-2085000</v>
+        <v>2085000</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>3711000</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>3235000</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/DOW_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOW_YR_FIN.xlsx
@@ -656,100 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>42964000</v>
+      </c>
+      <c r="E8" s="3">
         <v>44622000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>56902000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>54968000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>38542000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>42951000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>49604000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>43730000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>48158000</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -759,39 +762,42 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>38283000</v>
+      </c>
+      <c r="E9" s="3">
         <v>39565000</v>
       </c>
-      <c r="E9" s="3">
-        <v>48450000</v>
-      </c>
       <c r="F9" s="3">
+        <v>48338000</v>
+      </c>
+      <c r="G9" s="3">
         <v>44258000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>33346000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>36582000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>41074000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>36350000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>37668000</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,39 +807,42 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4681000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5057000</v>
       </c>
-      <c r="E10" s="3">
-        <v>8452000</v>
-      </c>
       <c r="F10" s="3">
+        <v>8564000</v>
+      </c>
+      <c r="G10" s="3">
         <v>10710000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5196000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6369000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8530000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7380000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10490000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,38 +874,39 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>810000</v>
+      </c>
+      <c r="E12" s="3">
         <v>829000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>851000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>857000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>768000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>765000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>800000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>803000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1593000</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,39 +961,42 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1128000</v>
+        <v>82000</v>
       </c>
       <c r="E14" s="3">
-        <v>-465000</v>
+        <v>1132000</v>
       </c>
       <c r="F14" s="3">
+        <v>-357000</v>
+      </c>
+      <c r="G14" s="3">
         <v>308000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-197000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4305000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1436000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3016000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2057000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,39 +1006,42 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>310000</v>
+      </c>
+      <c r="E15" s="3">
         <v>324000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>336000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>388000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>401000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>419000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>469000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>400000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>544000</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,38 +1070,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>41987000</v>
+        <v>40720000</v>
       </c>
       <c r="E17" s="3">
-        <v>50970000</v>
+        <v>41983000</v>
       </c>
       <c r="F17" s="3">
+        <v>50862000</v>
+      </c>
+      <c r="G17" s="3">
         <v>46816000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35883000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>39151000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>44002000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>40024000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>44815000</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,39 +1112,42 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2635000</v>
+        <v>2244000</v>
       </c>
       <c r="E18" s="3">
-        <v>5932000</v>
+        <v>2639000</v>
       </c>
       <c r="F18" s="3">
+        <v>6040000</v>
+      </c>
+      <c r="G18" s="3">
         <v>8152000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2659000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3800000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5602000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3706000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3343000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1128,9 +1157,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,38 +1179,39 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E20" s="3">
         <v>334000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-182000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-977000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-110000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-564000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-395000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1928000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1188,36 +1221,39 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2625000</v>
+        <v>2603000</v>
       </c>
       <c r="E21" s="3">
-        <v>6450000</v>
+        <v>2629000</v>
       </c>
       <c r="F21" s="3">
+        <v>6558000</v>
+      </c>
+      <c r="G21" s="3">
         <v>9517000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3064000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4329000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6635000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4501000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,39 +1266,42 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>811000</v>
+      </c>
+      <c r="E22" s="3">
         <v>746000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>662000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>731000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>827000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>933000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1063000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>914000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>858000</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1272,39 +1311,42 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1600000</v>
+      </c>
+      <c r="E23" s="3">
         <v>656000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6090000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8145000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2071000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1247000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3749000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>237000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4413000</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,39 +1356,42 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>399000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-4000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1450000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1740000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>777000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>470000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>809000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1524000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9000</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1356,9 +1401,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,39 +1446,42 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1201000</v>
+      </c>
+      <c r="E26" s="3">
         <v>660000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4640000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6405000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1294000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1717000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2940000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1287000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4404000</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,39 +1491,42 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1104000</v>
+      </c>
+      <c r="E27" s="3">
         <v>578000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4558000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6279000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1216000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1365000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4641000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>451000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3978000</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,9 +1536,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1543,17 +1603,17 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>445000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>1835000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>1882000</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,39 +1716,42 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-334000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>182000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>977000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>110000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>564000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>395000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1928000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1692,39 +1761,42 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1116000</v>
+      </c>
+      <c r="E33" s="3">
         <v>589000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4582000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6311000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1225000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1359000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4641000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>465000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3978000</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,9 +1806,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,39 +1851,42 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1116000</v>
+      </c>
+      <c r="E35" s="3">
         <v>589000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4582000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6311000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1225000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1359000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4641000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>465000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3978000</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,56 +1896,62 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,32 +1987,33 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2189000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2987000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3886000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2988000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5104000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2367000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2724000</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,35 +2029,38 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>383000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1301000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1044000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>246000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>45000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>29000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>100000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
@@ -1985,33 +2074,36 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6864000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6627000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7803000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9588000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7709000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7596000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9054000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,33 +2119,36 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6544000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6076000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6988000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7372000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5701000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6214000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6899000</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2069,33 +2164,36 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>536000</v>
+      </c>
+      <c r="E45" s="3">
         <v>562000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>702000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>609000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>521000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>596000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>20553000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2111,33 +2209,36 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16590000</v>
+      </c>
+      <c r="E46" s="3">
         <v>17614000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20477000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20848000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19084000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16815000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>39370000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2153,33 +2254,36 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4679000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4448000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5048000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5716000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4608000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5055000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6326000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2195,33 +2299,36 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23272000</v>
+      </c>
+      <c r="E48" s="3">
         <v>22386000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21669000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21967000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22095000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23068000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21418000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,35 +2344,38 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10286000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10713000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11086000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11645000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12260000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12555000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14071000</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,33 +2479,36 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>768000</v>
+      </c>
+      <c r="E52" s="3">
         <v>895000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1035000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>35000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>23000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17000</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2405,9 +2524,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,33 +2569,36 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>57312000</v>
+      </c>
+      <c r="E54" s="3">
         <v>57967000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>60603000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>62990000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>61470000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>60524000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>83699000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,9 +2614,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,32 +2655,33 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6541000</v>
+      </c>
+      <c r="E57" s="3">
         <v>6326000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7216000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8416000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5889000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5953000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6935000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,35 +2697,38 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>977000</v>
+      </c>
+      <c r="E58" s="3">
         <v>530000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1011000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>784000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1036000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1574000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>636000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2609,33 +2742,36 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>660000</v>
+      </c>
+      <c r="E59" s="3">
         <v>758000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>700000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1394000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1979000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1370000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5716000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2651,33 +2787,36 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10288000</v>
+      </c>
+      <c r="E60" s="3">
         <v>9957000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11331000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13226000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11108000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10679000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15547000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,33 +2832,36 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16695000</v>
+      </c>
+      <c r="E61" s="3">
         <v>15939000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15695000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15491000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18190000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17865000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>19317000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2735,33 +2877,36 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5870000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5990000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5687000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5546000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5199000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5849000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4469000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,33 +3057,36 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>39461000</v>
+      </c>
+      <c r="E66" s="3">
         <v>38859000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>39356000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>44251000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48465000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>46430000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>50078000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2945,9 +3102,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,33 +3301,36 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20909000</v>
+      </c>
+      <c r="E72" s="3">
         <v>21774000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>23180000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20623000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16361000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17045000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>35460000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,9 +3346,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,33 +3481,36 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17355000</v>
+      </c>
+      <c r="E76" s="3">
         <v>18607000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20718000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18165000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12435000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13541000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>32483000</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,9 +3526,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,86 +3571,92 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1116000</v>
+      </c>
+      <c r="E81" s="3">
         <v>589000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4582000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6311000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1225000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1359000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4641000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>465000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3978000</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,9 +3666,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,35 +3688,36 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2517000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2217000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2342000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2364000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2377000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2423000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2347000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2064000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,9 +3730,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,36 +3955,39 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2914000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5196000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7475000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7009000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6226000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5930000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4254000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4929000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3784,9 +4000,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,35 +4022,36 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3268000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2692000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2248000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2416000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1392000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2046000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2251000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3115000</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,9 +4064,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,36 +4154,39 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2368000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2928000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2970000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2914000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-841000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2192000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2195000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>7518000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3970,9 +4199,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,35 +4221,36 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1966000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1972000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2006000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2073000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2071000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2085000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3711000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3235000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,36 +4398,39 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1168000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3115000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3361000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6071000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2764000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4095000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5404000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3325000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,36 +4443,39 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-163000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-45000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-237000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-99000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>107000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-27000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-99000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>320000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4240,36 +4488,39 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-785000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-892000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>907000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2075000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2728000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-384000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3444000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-416000</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,7 +4533,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/DOW_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOW_YR_FIN.xlsx
@@ -656,106 +656,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>39968000</v>
+      </c>
+      <c r="E8" s="3">
         <v>42964000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>44622000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>56902000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>54968000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>38542000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>42951000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>49604000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>43730000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>48158000</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,42 +768,45 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>37477000</v>
+      </c>
+      <c r="E9" s="3">
         <v>38283000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>39565000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>48338000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>44258000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>33346000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>36582000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>41074000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>36350000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>37668000</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,42 +816,45 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2491000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4681000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5057000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8564000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10710000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5196000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6369000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8530000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7380000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10490000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,41 +887,42 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>752000</v>
+      </c>
+      <c r="E12" s="3">
         <v>810000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>829000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>851000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>857000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>768000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>765000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>800000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>803000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1593000</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,42 +980,45 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1656000</v>
+      </c>
+      <c r="E14" s="3">
         <v>82000</v>
       </c>
-      <c r="E14" s="3">
-        <v>1132000</v>
-      </c>
       <c r="F14" s="3">
+        <v>490000</v>
+      </c>
+      <c r="G14" s="3">
         <v>-357000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>308000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-197000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4305000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1436000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3016000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2057000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,42 +1028,45 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>231000</v>
+      </c>
+      <c r="E15" s="3">
         <v>310000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>324000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>336000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>388000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>401000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>419000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>469000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>400000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>544000</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,41 +1096,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40029000</v>
+      </c>
+      <c r="E17" s="3">
         <v>40720000</v>
       </c>
-      <c r="E17" s="3">
-        <v>41983000</v>
-      </c>
       <c r="F17" s="3">
+        <v>42625000</v>
+      </c>
+      <c r="G17" s="3">
         <v>50862000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>46816000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>35883000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>39151000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>44002000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>40024000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>44815000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1115,42 +1141,45 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2244000</v>
       </c>
-      <c r="E18" s="3">
-        <v>2639000</v>
-      </c>
       <c r="F18" s="3">
+        <v>1997000</v>
+      </c>
+      <c r="G18" s="3">
         <v>6040000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8152000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2659000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3800000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5602000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3706000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3343000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1160,9 +1189,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,41 +1212,42 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-49000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>334000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-182000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-977000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-110000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-564000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-395000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1928000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1224,39 +1257,42 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2603000</v>
       </c>
-      <c r="E21" s="3">
-        <v>2629000</v>
-      </c>
       <c r="F21" s="3">
+        <v>1987000</v>
+      </c>
+      <c r="G21" s="3">
         <v>6558000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9517000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3064000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4329000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6635000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4501000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,42 +1305,45 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>865000</v>
+      </c>
+      <c r="E22" s="3">
         <v>811000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>746000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>662000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>731000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>827000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>933000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1063000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>914000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>858000</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,42 +1353,45 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2511000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1600000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>656000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6090000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8145000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2071000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1247000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3749000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>237000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4413000</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,42 +1401,45 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="E24" s="3">
         <v>399000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1450000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1740000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>777000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>470000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>809000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1524000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9000</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1404,9 +1449,12 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,42 +1497,45 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2444000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1201000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>660000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4640000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6405000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1294000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1717000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2940000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1287000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4404000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1494,42 +1545,45 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2634000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1104000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>578000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4558000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6279000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1216000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1365000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4641000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>451000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3978000</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,9 +1593,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1606,17 +1666,17 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>445000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>1835000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>1882000</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,42 +1785,45 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="E32" s="3">
         <v>49000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-334000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>182000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>977000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>110000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>564000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>395000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1928000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1764,42 +1833,45 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2623000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1116000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>589000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4582000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6311000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1225000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1359000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4641000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>465000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3978000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,9 +1881,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,42 +1929,45 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2623000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1116000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>589000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4582000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6311000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1225000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1359000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4641000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>465000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3978000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1899,59 +1977,65 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,35 +2073,36 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3816000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2189000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2987000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3886000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2988000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5104000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2367000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2724000</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2032,38 +2118,41 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>454000</v>
+      </c>
+      <c r="E42" s="3">
         <v>383000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1301000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1044000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>246000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>45000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>29000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>100000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
@@ -2077,36 +2166,39 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6638000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6864000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6627000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7803000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9588000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7709000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7596000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9054000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,36 +2214,39 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6595000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6544000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6076000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6988000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7372000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5701000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6214000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6899000</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2167,36 +2262,39 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>423000</v>
+      </c>
+      <c r="E45" s="3">
         <v>536000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>562000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>702000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>609000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>521000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>596000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>20553000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2212,36 +2310,39 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18062000</v>
+      </c>
+      <c r="E46" s="3">
         <v>16590000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17614000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20477000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20848000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19084000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16815000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>39370000</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2257,36 +2358,39 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4591000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4679000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4448000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5048000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5716000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4608000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5055000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6326000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,36 +2406,39 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23606000</v>
+      </c>
+      <c r="E48" s="3">
         <v>23272000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22386000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21669000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21967000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22095000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23068000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21418000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2347,38 +2454,41 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9464000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10286000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10713000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11086000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11645000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12260000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12555000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14071000</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,36 +2598,39 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>768000</v>
+        <v>8000</v>
       </c>
       <c r="E52" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F52" s="3">
         <v>895000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1035000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>35000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>23000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>17000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2527,9 +2646,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,36 +2694,39 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>58538000</v>
+      </c>
+      <c r="E54" s="3">
         <v>57312000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>57967000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>60603000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>62990000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>61470000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>60524000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>83699000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2617,9 +2742,12 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,35 +2785,36 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5545000</v>
+      </c>
+      <c r="E57" s="3">
         <v>6541000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6326000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7216000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8416000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5889000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5953000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6935000</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,38 +2830,41 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>656000</v>
+      </c>
+      <c r="E58" s="3">
         <v>977000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>530000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1011000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>784000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1036000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1574000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>636000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2745,36 +2878,39 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>792000</v>
+      </c>
+      <c r="E59" s="3">
         <v>660000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>758000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>700000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1394000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1979000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1370000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5716000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,36 +2926,39 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9183000</v>
+      </c>
+      <c r="E60" s="3">
         <v>10288000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9957000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11331000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13226000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11108000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10679000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15547000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,36 +2974,39 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18946000</v>
+      </c>
+      <c r="E61" s="3">
         <v>16695000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15939000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15695000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15491000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18190000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17865000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>19317000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2880,36 +3022,39 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6102000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5870000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5990000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5687000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5546000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5199000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5849000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4469000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,36 +3214,39 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41016000</v>
+      </c>
+      <c r="E66" s="3">
         <v>39461000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>38859000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39356000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>44251000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48465000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>46430000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>50078000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,9 +3262,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,36 +3474,39 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16781000</v>
+      </c>
+      <c r="E72" s="3">
         <v>20909000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>21774000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>23180000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>20623000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16361000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>17045000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>35460000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,9 +3522,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,36 +3666,39 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16008000</v>
+      </c>
+      <c r="E76" s="3">
         <v>17355000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18607000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20718000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18165000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12435000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13541000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>32483000</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3529,9 +3714,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,92 +3762,98 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2623000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1116000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>589000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4582000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6311000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1225000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1359000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4641000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>465000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3978000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3669,9 +3863,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,38 +3886,39 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2533000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2517000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2217000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2342000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2364000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2377000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2423000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2347000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2064000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3733,9 +3931,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,39 +4171,42 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1032000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2914000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5196000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7475000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7009000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6226000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5930000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4254000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4929000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,9 +4219,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,38 +4242,39 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2636000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3268000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2692000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2248000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2416000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1392000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2046000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2251000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3115000</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,9 +4287,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,39 +4383,42 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2126000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2368000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2928000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2970000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2914000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-841000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2192000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2195000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>7518000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4202,9 +4431,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,38 +4454,39 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1490000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1966000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1972000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2006000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2073000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2071000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2085000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3711000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>3235000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,39 +4643,42 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2508000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1168000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3115000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3361000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6071000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2764000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4095000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5404000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3325000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4446,39 +4691,42 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-163000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-45000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-237000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-99000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>107000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-27000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-99000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>320000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4491,39 +4739,42 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1689000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-785000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-892000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>907000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2075000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2728000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-384000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3444000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-416000</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4536,7 +4787,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/DOW_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOW_YR_FIN.xlsx
@@ -4252,7 +4252,7 @@
         <v>-2636000</v>
       </c>
       <c r="E91" s="3">
-        <v>-3268000</v>
+        <v>-3143000</v>
       </c>
       <c r="F91" s="3">
         <v>-2692000</v>
